--- a/assets/constructions/examples/ctd_tgm_face.xlsx
+++ b/assets/constructions/examples/ctd_tgm_face.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD6"/>
+  <dimension ref="A1:AH6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -579,48 +579,76 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>VGFL-75100-T12-4C</t>
+          <t>WMTWGML522B100-205</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>VARGUS</t>
+          <t>WIDIA</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VG-Cut</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
+          <t>WMT</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>WID_WMT..05</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>VARGUS</t>
+          <t>WIDIA</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>12</v>
-      </c>
-      <c r="G2" t="inlineStr"/>
+        <v>22</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>WMT..05</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>VARGUS_VG_CUT_HPCL</t>
+          <t>WIDIA_GML</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>VARGUS_VGD:4</t>
+          <t>WIDIA_WMT:05</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>69.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="K2" t="n">
-        <v>99.59999999999999</v>
+        <v>205</v>
       </c>
       <c r="L2" t="n">
         <v>2</v>
@@ -637,25 +665,23 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>3</v>
-      </c>
-      <c r="R2" t="n">
-        <v>47</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="b">
@@ -676,14 +702,20 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>2019 / Groovex Catalog</t>
-        </is>
-      </c>
+          <t>2017 / WIDIA Catalogue</t>
+        </is>
+      </c>
+      <c r="AE2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>VGFR-75130-T22-5C</t>
+          <t>VGFR-150-&gt;-T12-4C</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -703,7 +735,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
@@ -713,14 +745,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>VARGUS_VGD:5</t>
+          <t>VARGUS_VGD:4</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>70.3</v>
+        <v>134.5</v>
       </c>
       <c r="K3" t="n">
-        <v>143.9</v>
+        <v>285.5</v>
       </c>
       <c r="L3" t="n">
         <v>2</v>
@@ -743,19 +775,19 @@
         <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V3" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="b">
@@ -778,57 +810,63 @@
         <is>
           <t>2019 / Groovex Catalog</t>
         </is>
+      </c>
+      <c r="AE3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>330.55</v>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AH3" t="n">
+        <v>30388.68</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>WMTWGML419B100-205</t>
+          <t>VGFR-75100-T10-3C</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>WIDIA</t>
+          <t>VARGUS</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>WMT</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>WID_WMT..04</t>
-        </is>
-      </c>
+          <t>VG-Cut</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>WIDIA</t>
+          <t>VARGUS</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>19.05</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>WMT..04</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>WIDIA_GML</t>
+          <t>VARGUS_VG_CUT_HPCR</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>WIDIA_WMT:04</t>
+          <t>VARGUS_VGD:3</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>100</v>
+        <v>73.7</v>
       </c>
       <c r="K4" t="n">
-        <v>205</v>
+        <v>103.2</v>
       </c>
       <c r="L4" t="n">
         <v>2</v>
@@ -841,27 +879,29 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="R4" t="n">
+        <v>45</v>
+      </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V4" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="b">
@@ -882,14 +922,28 @@
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>2017 / WIDIA Catalogue</t>
-        </is>
+          <t>2019 / Groovex Catalog</t>
+        </is>
+      </c>
+      <c r="AE4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>330.55</v>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AH4" t="n">
+        <v>30388.68</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>VGFL-3048-T24-4C</t>
+          <t>VGFR-4860-T10-3C</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -909,24 +963,24 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>VARGUS_VG_CUT_HPCL</t>
+          <t>VARGUS_VG_CUT_HPCR</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>VARGUS_VGD:4</t>
+          <t>VARGUS_VGD:3</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>27.6</v>
+        <v>46.6</v>
       </c>
       <c r="K5" t="n">
-        <v>49</v>
+        <v>62.8</v>
       </c>
       <c r="L5" t="n">
         <v>2</v>
@@ -939,7 +993,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -949,19 +1003,19 @@
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V5" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="b">
@@ -984,57 +1038,63 @@
         <is>
           <t>2019 / Groovex Catalog</t>
         </is>
+      </c>
+      <c r="AE5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>330.55</v>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AH5" t="n">
+        <v>30388.68</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>WMTWGML522B100-205</t>
+          <t>VGFL-2530-T10-3C</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>WIDIA</t>
+          <t>VARGUS</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>WMT</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>WID_WMT..05</t>
-        </is>
-      </c>
+          <t>VG-Cut</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>WIDIA</t>
+          <t>VARGUS</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>22</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>WMT..05</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>WIDIA_GML</t>
+          <t>VARGUS_VG_CUT_HPCL</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>WIDIA_WMT:05</t>
+          <t>VARGUS_VGD:3</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>100</v>
+        <v>23.5</v>
       </c>
       <c r="K6" t="n">
-        <v>205</v>
+        <v>32</v>
       </c>
       <c r="L6" t="n">
         <v>2</v>
@@ -1051,23 +1111,25 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="R6" t="n">
+        <v>45</v>
+      </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="V6" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="b">
@@ -1088,8 +1150,22 @@
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>2017 / WIDIA Catalogue</t>
-        </is>
+          <t>2019 / Groovex Catalog</t>
+        </is>
+      </c>
+      <c r="AE6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>330.55</v>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AH6" t="n">
+        <v>30388.68</v>
       </c>
     </row>
   </sheetData>
